--- a/2_Test_Scenarios_and_Test_Cases_and_Bug_Reports.xlsx
+++ b/2_Test_Scenarios_and_Test_Cases_and_Bug_Reports.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\my things\SQA projects\Manual_Testing_of_ChatGPT_Web_Application\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277F3D17-9B2E-40EA-ACAE-2625BE24DCBA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{114BBAAC-6689-4A93-930E-977C3A11EC40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="633" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="633" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Test Scenarios" sheetId="1" r:id="rId1"/>
@@ -513,9 +513,6 @@
     <t>User has successfully logged in and has access to ChatGPT</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_1.jpg</t>
-  </si>
-  <si>
     <t>Valid email: sqatestingpractice@gmail.com</t>
   </si>
   <si>
@@ -532,9 +529,6 @@
     <t>Appropriate error message "invalid email" should be displayed on "email-verification" page and login should fail</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_2.jpg</t>
-  </si>
-  <si>
     <t>User is on the login page</t>
   </si>
   <si>
@@ -550,15 +544,9 @@
     <t>The user is logged out and sent to the login page</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_3.jpg</t>
-  </si>
-  <si>
     <t>User is already logged into ChatGPT</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_4.jpg</t>
-  </si>
-  <si>
     <t>1. Refresh the page</t>
   </si>
   <si>
@@ -566,9 +554,6 @@
   </si>
   <si>
     <t>Prompt should be sent successfully and AI should generate a response</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_5.jpg</t>
   </si>
   <si>
     <t>User is logged in</t>
@@ -579,9 +564,6 @@
 3. Observe the response</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_6.jpg</t>
-  </si>
-  <si>
     <t>AI should generate a relevant response</t>
   </si>
   <si>
@@ -616,9 +598,6 @@
     <t>AI maintain conversation context and provide an appropriate response</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_7.jpg</t>
-  </si>
-  <si>
     <t>1. Click on regenerate button at the end of the AI response
 2. Click on "Try again" option
 3. Observe the response</t>
@@ -627,9 +606,6 @@
     <t>A new AI response should be generated successfully</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_8.jpg</t>
-  </si>
-  <si>
     <t>A new AI response is generated successfully</t>
   </si>
   <si>
@@ -644,19 +620,10 @@
     <t>AI process the long prompt without errors</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_9.jpg</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_10.jpg</t>
-  </si>
-  <si>
     <t>AI process the prompt correctly without crashing</t>
   </si>
   <si>
     <t>AI should process the prompt correctly without crashing</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_11.jpg</t>
   </si>
   <si>
     <t>A new conversation should appear in the history panel</t>
@@ -682,9 +649,6 @@
     <t>A meaningful conversation title should be generated automatically</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_12.jpg</t>
-  </si>
-  <si>
     <t>A meaningful conversation title is generated automatically</t>
   </si>
   <si>
@@ -704,9 +668,6 @@
   </si>
   <si>
     <t>Selected conversation open correctly</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_13.jpg</t>
   </si>
   <si>
     <t>Existing conversation available</t>
@@ -729,9 +690,6 @@
     <t>Conversation name update successfully</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_14.jpg</t>
-  </si>
-  <si>
     <t>1. Verify user chat panel is open
 2. Go to a chat
 3. Verify the 3 dots in the end of the chat conversation title
@@ -746,9 +704,6 @@
     <t>Conversation (Hello ChatGPT) is removed from history</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_15.jpg</t>
-  </si>
-  <si>
     <t>1. Open a existing chat with conversations
 2. Refresh the page</t>
   </si>
@@ -762,12 +717,6 @@
     <t>Previous conversations remain available after refreshing</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_16.jpg</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_17.jpg</t>
-  </si>
-  <si>
     <t>User is on chat screen</t>
   </si>
   <si>
@@ -797,16 +746,10 @@
     <t>A new line is inserted instead of sending the message</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_18.jpg</t>
-  </si>
-  <si>
     <t>Prompt should be submitted successfully</t>
   </si>
   <si>
     <t>Prompt is submitted successfully</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_19.jpg</t>
   </si>
   <si>
     <t>"Explain Software Testing"</t>
@@ -828,9 +771,6 @@
     <t>Emoji is accepted and processed correctly</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_20.jpg</t>
-  </si>
-  <si>
     <t>User copied text from another source</t>
   </si>
   <si>
@@ -848,9 +788,6 @@
     <t>Pasted text appear correctly in the prompt box</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_21.jpg</t>
-  </si>
-  <si>
     <t xml:space="preserve">1. Enter a long prompt
 2. Observe the the behavior </t>
   </si>
@@ -858,9 +795,6 @@
     <t>Prompt convert into a DOC file</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_22.jpg</t>
-  </si>
-  <si>
     <t>Prompt should be usable in text form without any UI issues</t>
   </si>
   <si>
@@ -870,16 +804,10 @@
     <t>Settings panel open without errors</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_23.jpg</t>
-  </si>
-  <si>
     <t>User profile information should be displayed correctly</t>
   </si>
   <si>
     <t>User profile information is displayed correctly</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_24.jpg</t>
   </si>
   <si>
     <t>Selected theme should be applied successfully</t>
@@ -914,9 +842,6 @@
     <t>Selected theme is applied successfully</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_25.jpg</t>
-  </si>
-  <si>
     <t>Theme already changed</t>
   </si>
   <si>
@@ -929,9 +854,6 @@
     <t>Previously selected theme remain active</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_26.jpg</t>
-  </si>
-  <si>
     <t>AI response already generated</t>
   </si>
   <si>
@@ -939,9 +861,6 @@
   </si>
   <si>
     <t>Response is copied to the notepad successfully</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_27.jpg</t>
   </si>
   <si>
     <t>AI is generating response</t>
@@ -961,9 +880,6 @@
     <t>1. Click on the stop generating button which appears in the message box while generating response</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_28.jpg</t>
-  </si>
-  <si>
     <t>AI is stoped generating the response</t>
   </si>
   <si>
@@ -975,9 +891,6 @@
 3. Observe the response</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_29.jpg</t>
-  </si>
-  <si>
     <t>Copied content should retain its formatting as expected</t>
   </si>
   <si>
@@ -999,9 +912,6 @@
   </si>
   <si>
     <t>Copied content retain its formatting as expected</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_30.jpg</t>
   </si>
   <si>
     <t>User logged in and prompt box available</t>
@@ -1057,9 +967,6 @@
     <t>Prompt box remain active and ready for the next input</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_31.jpg</t>
-  </si>
-  <si>
     <t>Placeholder text is visible when the prompt box is empty</t>
   </si>
   <si>
@@ -1067,9 +974,6 @@
 2. Verify the prompt box is empty</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_32.jpg</t>
-  </si>
-  <si>
     <t>"Testing Prompt"</t>
   </si>
   <si>
@@ -1083,9 +987,6 @@
     <t>Send button should activate only after input is entered</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_33.jpg</t>
-  </si>
-  <si>
     <t>1. Observe the changes after submitting a prompt in the prompt box</t>
   </si>
   <si>
@@ -1093,9 +994,6 @@
   </si>
   <si>
     <t>Prompt box is cleared automatically after sending a prompt</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_34.jpg</t>
   </si>
   <si>
     <t>1. Create new conversation
@@ -1105,20 +1003,11 @@
     <t>Most recent conversation appear first</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_35.jpg</t>
-  </si>
-  <si>
     <t>1. Delete conversation chat from the history panel
 2. Observe the changes on the history panel</t>
   </si>
   <si>
     <t>Deleted conversation is not visible in the history list</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_36.jpg</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_37.jpg</t>
   </si>
   <si>
     <t>1. Right-click anywhere on the webpage and select Inspect
@@ -1141,19 +1030,10 @@
     <t>User is able to navigate the interface using only the keyboard</t>
   </si>
   <si>
-    <t>All Attachments\TC_A_38.jpg</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_39.jpg</t>
-  </si>
-  <si>
     <t>1. Right-click anywhere on the webpage and select Inspect
 2. Click the Toggle device toolbar icon in the top-left corner of the developer panel
 3. Simulate 3G network
 4. Send a prompt</t>
-  </si>
-  <si>
-    <t>All Attachments\TC_A_40.jpg</t>
   </si>
   <si>
     <t>Application continue functioning with acceptable performance under a slow network</t>
@@ -1269,6 +1149,126 @@
   </si>
   <si>
     <t>Large text input is automatically converted into a document attachment</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_1.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_2.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_3.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_4.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_5.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_6.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_7.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_8.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_9.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_10.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_11.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_12.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_13.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_14.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_15.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_16.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_17.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_18.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_19.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_20.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_21.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_22.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_23.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_24.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_25.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_26.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_27.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_28.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_29.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_30.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_31.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_32.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_33.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_34.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_35.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_36.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_37.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_38.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_39.jpg</t>
+  </si>
+  <si>
+    <t>All_Attachments\TC_A_40.jpg</t>
   </si>
 </sst>
 </file>
@@ -2356,7 +2356,7 @@
         <v>27</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>366</v>
+        <v>326</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>28</v>
@@ -2373,7 +2373,7 @@
         <v>31</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>367</v>
+        <v>327</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>28</v>
@@ -2390,7 +2390,7 @@
         <v>34</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>368</v>
+        <v>328</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>28</v>
@@ -2407,7 +2407,7 @@
         <v>37</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>369</v>
+        <v>329</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>28</v>
@@ -2424,7 +2424,7 @@
         <v>39</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>370</v>
+        <v>330</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>40</v>
@@ -2441,7 +2441,7 @@
         <v>31</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>371</v>
+        <v>331</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>40</v>
@@ -2452,13 +2452,13 @@
         <v>43</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>378</v>
+        <v>338</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>372</v>
+        <v>332</v>
       </c>
       <c r="E17" s="1" t="s">
         <v>28</v>
@@ -2469,13 +2469,13 @@
         <v>44</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>379</v>
+        <v>339</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>373</v>
+        <v>333</v>
       </c>
       <c r="E18" s="1" t="s">
         <v>28</v>
@@ -2492,7 +2492,7 @@
         <v>47</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>374</v>
+        <v>334</v>
       </c>
       <c r="E19" s="1" t="s">
         <v>40</v>
@@ -2509,7 +2509,7 @@
         <v>47</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>375</v>
+        <v>335</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>40</v>
@@ -2526,7 +2526,7 @@
         <v>52</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>376</v>
+        <v>336</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>40</v>
@@ -2543,7 +2543,7 @@
         <v>55</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>377</v>
+        <v>337</v>
       </c>
       <c r="E22" s="1" t="s">
         <v>28</v>
@@ -2587,7 +2587,7 @@
     <col min="11" max="11" width="34.88671875" customWidth="1"/>
     <col min="12" max="12" width="36.109375" customWidth="1"/>
     <col min="13" max="13" width="12" customWidth="1"/>
-    <col min="14" max="14" width="19.6640625" customWidth="1"/>
+    <col min="14" max="14" width="25.44140625" customWidth="1"/>
     <col min="15" max="15" width="13.33203125" customWidth="1"/>
     <col min="16" max="16" width="11.6640625" customWidth="1"/>
   </cols>
@@ -2668,7 +2668,7 @@
     </row>
     <row r="11" spans="1:15" ht="31.2" x14ac:dyDescent="0.6">
       <c r="A11" s="39" t="s">
-        <v>350</v>
+        <v>310</v>
       </c>
       <c r="B11" s="39"/>
       <c r="C11" s="39"/>
@@ -2755,13 +2755,13 @@
         <v>28</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="I14" s="8" t="s">
         <v>157</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="K14" s="8" t="s">
         <v>158</v>
@@ -2773,7 +2773,7 @@
         <v>156</v>
       </c>
       <c r="N14" s="5" t="s">
-        <v>160</v>
+        <v>345</v>
       </c>
       <c r="O14" s="1" t="s">
         <v>143</v>
@@ -2784,7 +2784,7 @@
         <v>63</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>25</v>
@@ -2802,28 +2802,28 @@
         <v>28</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="I15" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="J15" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="K15" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="L15" s="8" t="s">
         <v>162</v>
-      </c>
-      <c r="J15" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="K15" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="L15" s="8" t="s">
-        <v>163</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>155</v>
       </c>
       <c r="N15" s="5" t="s">
-        <v>166</v>
+        <v>346</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>380</v>
+        <v>340</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
@@ -2849,31 +2849,31 @@
         <v>28</v>
       </c>
       <c r="H16" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="J16" s="8" t="s">
+        <v>143</v>
+      </c>
+      <c r="K16" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="L16" s="8" t="s">
         <v>169</v>
-      </c>
-      <c r="I16" s="8" t="s">
-        <v>271</v>
-      </c>
-      <c r="J16" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="K16" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="L16" s="8" t="s">
-        <v>171</v>
       </c>
       <c r="M16" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N16" s="5" t="s">
-        <v>172</v>
+        <v>347</v>
       </c>
       <c r="O16" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="17" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A17" s="9" t="s">
         <v>66</v>
       </c>
@@ -2896,25 +2896,25 @@
         <v>40</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I17" s="8" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="J17" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="M17" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N17" s="5" t="s">
-        <v>174</v>
+        <v>348</v>
       </c>
       <c r="O17" s="1" t="s">
         <v>143</v>
@@ -2943,25 +2943,25 @@
         <v>28</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I18" s="8" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="J18" s="8" t="s">
         <v>144</v>
       </c>
       <c r="K18" s="8" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="L18" s="8" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="M18" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N18" s="5" t="s">
-        <v>178</v>
+        <v>349</v>
       </c>
       <c r="O18" s="1" t="s">
         <v>143</v>
@@ -2990,25 +2990,25 @@
         <v>28</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I19" s="8" t="s">
-        <v>187</v>
+        <v>181</v>
       </c>
       <c r="J19" s="8" t="s">
         <v>145</v>
       </c>
       <c r="K19" s="8" t="s">
-        <v>182</v>
+        <v>176</v>
       </c>
       <c r="L19" s="8" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="M19" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N19" s="5" t="s">
-        <v>181</v>
+        <v>350</v>
       </c>
       <c r="O19" s="1" t="s">
         <v>143</v>
@@ -3037,25 +3037,25 @@
         <v>28</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>186</v>
+        <v>180</v>
       </c>
       <c r="I20" s="8" t="s">
-        <v>188</v>
+        <v>182</v>
       </c>
       <c r="J20" s="8" t="s">
         <v>146</v>
       </c>
       <c r="K20" s="8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="L20" s="8" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N20" s="5" t="s">
-        <v>192</v>
+        <v>351</v>
       </c>
       <c r="O20" s="1" t="s">
         <v>143</v>
@@ -3084,25 +3084,25 @@
         <v>40</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="I21" s="8" t="s">
-        <v>193</v>
+        <v>186</v>
       </c>
       <c r="J21" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K21" s="8" t="s">
-        <v>194</v>
+        <v>187</v>
       </c>
       <c r="L21" s="8" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="M21" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N21" s="5" t="s">
-        <v>195</v>
+        <v>352</v>
       </c>
       <c r="O21" s="1" t="s">
         <v>143</v>
@@ -3131,25 +3131,25 @@
         <v>40</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I22" s="8" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="J22" s="8" t="s">
         <v>147</v>
       </c>
       <c r="K22" s="8" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="L22" s="8" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N22" s="5" t="s">
-        <v>200</v>
+        <v>353</v>
       </c>
       <c r="O22" s="1" t="s">
         <v>143</v>
@@ -3178,25 +3178,25 @@
         <v>99</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I23" s="8" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="J23" s="8" t="s">
         <v>148</v>
       </c>
       <c r="K23" s="8" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="L23" s="8" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="M23" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N23" s="5" t="s">
-        <v>201</v>
+        <v>354</v>
       </c>
       <c r="O23" s="1" t="s">
         <v>143</v>
@@ -3225,25 +3225,25 @@
         <v>28</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I24" s="8" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="J24" s="8" t="s">
         <v>149</v>
       </c>
       <c r="K24" s="8" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="L24" s="8" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="M24" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N24" s="5" t="s">
-        <v>204</v>
+        <v>355</v>
       </c>
       <c r="O24" s="1" t="s">
         <v>143</v>
@@ -3272,31 +3272,31 @@
         <v>99</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="I25" s="8" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="J25" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K25" s="8" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="L25" s="8" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="M25" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N25" s="5" t="s">
-        <v>211</v>
+        <v>356</v>
       </c>
       <c r="O25" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="26" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A26" s="9" t="s">
         <v>84</v>
       </c>
@@ -3319,25 +3319,25 @@
         <v>28</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="I26" s="8" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="J26" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K26" s="8" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="L26" s="8" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="M26" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N26" s="5" t="s">
-        <v>218</v>
+        <v>357</v>
       </c>
       <c r="O26" s="1" t="s">
         <v>143</v>
@@ -3366,25 +3366,25 @@
         <v>40</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="I27" s="8" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="J27" s="8" t="s">
-        <v>221</v>
+        <v>208</v>
       </c>
       <c r="K27" s="10" t="s">
-        <v>222</v>
+        <v>209</v>
       </c>
       <c r="L27" s="10" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="M27" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N27" s="5" t="s">
-        <v>224</v>
+        <v>358</v>
       </c>
       <c r="O27" s="1" t="s">
         <v>143</v>
@@ -3413,31 +3413,31 @@
         <v>28</v>
       </c>
       <c r="H28" s="11" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="I28" s="8" t="s">
-        <v>225</v>
+        <v>211</v>
       </c>
       <c r="J28" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K28" s="10" t="s">
-        <v>226</v>
+        <v>212</v>
       </c>
       <c r="L28" s="10" t="s">
-        <v>227</v>
+        <v>213</v>
       </c>
       <c r="M28" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N28" s="5" t="s">
-        <v>228</v>
+        <v>359</v>
       </c>
       <c r="O28" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="29" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A29" s="9" t="s">
         <v>90</v>
       </c>
@@ -3460,31 +3460,31 @@
         <v>40</v>
       </c>
       <c r="H29" s="11" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="I29" s="8" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="J29" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K29" s="10" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="L29" s="10" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N29" s="5" t="s">
-        <v>233</v>
+        <v>360</v>
       </c>
       <c r="O29" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="30" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A30" s="9" t="s">
         <v>92</v>
       </c>
@@ -3507,36 +3507,36 @@
         <v>28</v>
       </c>
       <c r="H30" s="11" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="I30" s="8" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="J30" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K30" s="10" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="L30" s="10" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N30" s="5" t="s">
-        <v>234</v>
+        <v>361</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="31" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A31" s="9" t="s">
         <v>94</v>
       </c>
       <c r="B31" s="10" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>35</v>
@@ -3554,25 +3554,25 @@
         <v>99</v>
       </c>
       <c r="H31" s="11" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="I31" s="8" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="J31" s="8" t="s">
-        <v>241</v>
+        <v>224</v>
       </c>
       <c r="K31" s="10" t="s">
-        <v>242</v>
+        <v>225</v>
       </c>
       <c r="L31" s="10" t="s">
-        <v>243</v>
+        <v>226</v>
       </c>
       <c r="M31" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N31" s="5" t="s">
-        <v>244</v>
+        <v>362</v>
       </c>
       <c r="O31" s="1" t="s">
         <v>143</v>
@@ -3601,25 +3601,25 @@
         <v>28</v>
       </c>
       <c r="H32" s="11" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="I32" s="8" t="s">
-        <v>249</v>
+        <v>230</v>
       </c>
       <c r="J32" s="8" t="s">
-        <v>248</v>
+        <v>229</v>
       </c>
       <c r="K32" s="10" t="s">
-        <v>245</v>
+        <v>227</v>
       </c>
       <c r="L32" s="10" t="s">
-        <v>246</v>
+        <v>228</v>
       </c>
       <c r="M32" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N32" s="5" t="s">
-        <v>247</v>
+        <v>363</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>143</v>
@@ -3648,25 +3648,25 @@
         <v>99</v>
       </c>
       <c r="H33" s="11" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="I33" s="8" t="s">
-        <v>250</v>
+        <v>231</v>
       </c>
       <c r="J33" s="8" t="s">
         <v>150</v>
       </c>
       <c r="K33" s="10" t="s">
-        <v>251</v>
+        <v>232</v>
       </c>
       <c r="L33" s="8" t="s">
-        <v>252</v>
+        <v>233</v>
       </c>
       <c r="M33" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N33" s="5" t="s">
-        <v>253</v>
+        <v>364</v>
       </c>
       <c r="O33" s="1" t="s">
         <v>143</v>
@@ -3695,31 +3695,31 @@
         <v>99</v>
       </c>
       <c r="H34" s="11" t="s">
-        <v>254</v>
+        <v>234</v>
       </c>
       <c r="I34" s="8" t="s">
-        <v>256</v>
+        <v>236</v>
       </c>
       <c r="J34" s="8" t="s">
-        <v>255</v>
+        <v>235</v>
       </c>
       <c r="K34" s="10" t="s">
-        <v>257</v>
+        <v>237</v>
       </c>
       <c r="L34" s="10" t="s">
-        <v>258</v>
+        <v>238</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N34" s="5" t="s">
-        <v>259</v>
+        <v>365</v>
       </c>
       <c r="O34" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="35" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A35" s="9" t="s">
         <v>102</v>
       </c>
@@ -3742,28 +3742,28 @@
         <v>99</v>
       </c>
       <c r="H35" s="11" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="I35" s="8" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="J35" s="8" t="s">
         <v>151</v>
       </c>
       <c r="K35" s="10" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="L35" s="10" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="M35" s="1" t="s">
         <v>155</v>
       </c>
       <c r="N35" s="5" t="s">
-        <v>262</v>
+        <v>366</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>381</v>
+        <v>341</v>
       </c>
     </row>
     <row r="36" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
@@ -3789,25 +3789,25 @@
         <v>40</v>
       </c>
       <c r="H36" s="11" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I36" s="8" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="J36" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K36" s="10" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="L36" s="10" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="M36" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N36" s="5" t="s">
-        <v>266</v>
+        <v>367</v>
       </c>
       <c r="O36" s="1" t="s">
         <v>143</v>
@@ -3836,25 +3836,25 @@
         <v>99</v>
       </c>
       <c r="H37" s="11" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I37" s="8" t="s">
-        <v>273</v>
+        <v>249</v>
       </c>
       <c r="J37" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K37" s="10" t="s">
-        <v>267</v>
+        <v>244</v>
       </c>
       <c r="L37" s="10" t="s">
-        <v>268</v>
+        <v>245</v>
       </c>
       <c r="M37" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N37" s="5" t="s">
-        <v>269</v>
+        <v>368</v>
       </c>
       <c r="O37" s="1" t="s">
         <v>143</v>
@@ -3883,31 +3883,31 @@
         <v>40</v>
       </c>
       <c r="H38" s="11" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="I38" s="8" t="s">
-        <v>274</v>
+        <v>250</v>
       </c>
       <c r="J38" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K38" s="10" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="L38" s="10" t="s">
-        <v>275</v>
+        <v>251</v>
       </c>
       <c r="M38" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N38" s="5" t="s">
-        <v>276</v>
+        <v>369</v>
       </c>
       <c r="O38" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="39" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A39" s="9" t="s">
         <v>110</v>
       </c>
@@ -3930,25 +3930,25 @@
         <v>99</v>
       </c>
       <c r="H39" s="11" t="s">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="I39" s="8" t="s">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="J39" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K39" s="10" t="s">
-        <v>279</v>
+        <v>254</v>
       </c>
       <c r="L39" s="10" t="s">
-        <v>280</v>
+        <v>255</v>
       </c>
       <c r="M39" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N39" s="5" t="s">
-        <v>281</v>
+        <v>370</v>
       </c>
       <c r="O39" s="1" t="s">
         <v>143</v>
@@ -3977,25 +3977,25 @@
         <v>99</v>
       </c>
       <c r="H40" s="11" t="s">
-        <v>282</v>
+        <v>256</v>
       </c>
       <c r="I40" s="8" t="s">
-        <v>289</v>
+        <v>262</v>
       </c>
       <c r="J40" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K40" s="10" t="s">
-        <v>283</v>
+        <v>257</v>
       </c>
       <c r="L40" s="10" t="s">
-        <v>284</v>
+        <v>258</v>
       </c>
       <c r="M40" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N40" s="5" t="s">
-        <v>285</v>
+        <v>371</v>
       </c>
       <c r="O40" s="1" t="s">
         <v>143</v>
@@ -4024,25 +4024,25 @@
         <v>28</v>
       </c>
       <c r="H41" s="11" t="s">
-        <v>286</v>
+        <v>259</v>
       </c>
       <c r="I41" s="8" t="s">
-        <v>290</v>
+        <v>263</v>
       </c>
       <c r="J41" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K41" s="10" t="s">
-        <v>287</v>
+        <v>260</v>
       </c>
       <c r="L41" s="10" t="s">
-        <v>288</v>
+        <v>261</v>
       </c>
       <c r="M41" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N41" s="5" t="s">
-        <v>291</v>
+        <v>372</v>
       </c>
       <c r="O41" s="1" t="s">
         <v>143</v>
@@ -4053,7 +4053,7 @@
         <v>116</v>
       </c>
       <c r="B42" s="10" t="s">
-        <v>293</v>
+        <v>265</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>41</v>
@@ -4071,25 +4071,25 @@
         <v>40</v>
       </c>
       <c r="H42" s="11" t="s">
-        <v>292</v>
+        <v>264</v>
       </c>
       <c r="I42" s="8" t="s">
-        <v>294</v>
+        <v>266</v>
       </c>
       <c r="J42" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K42" s="10" t="s">
-        <v>298</v>
+        <v>269</v>
       </c>
       <c r="L42" s="10" t="s">
-        <v>299</v>
+        <v>270</v>
       </c>
       <c r="M42" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N42" s="5" t="s">
-        <v>295</v>
+        <v>373</v>
       </c>
       <c r="O42" s="1" t="s">
         <v>143</v>
@@ -4118,25 +4118,25 @@
         <v>99</v>
       </c>
       <c r="H43" s="11" t="s">
-        <v>297</v>
+        <v>268</v>
       </c>
       <c r="I43" s="8" t="s">
-        <v>300</v>
+        <v>271</v>
       </c>
       <c r="J43" s="8" t="s">
-        <v>301</v>
+        <v>272</v>
       </c>
       <c r="K43" s="10" t="s">
-        <v>296</v>
+        <v>267</v>
       </c>
       <c r="L43" s="10" t="s">
-        <v>302</v>
+        <v>273</v>
       </c>
       <c r="M43" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N43" s="5" t="s">
-        <v>303</v>
+        <v>374</v>
       </c>
       <c r="O43" s="1" t="s">
         <v>143</v>
@@ -4165,31 +4165,31 @@
         <v>40</v>
       </c>
       <c r="H44" s="11" t="s">
-        <v>304</v>
+        <v>274</v>
       </c>
       <c r="I44" s="8" t="s">
-        <v>318</v>
+        <v>288</v>
       </c>
       <c r="J44" s="8" t="s">
-        <v>317</v>
+        <v>287</v>
       </c>
       <c r="K44" s="10" t="s">
-        <v>309</v>
+        <v>279</v>
       </c>
       <c r="L44" s="10" t="s">
-        <v>319</v>
+        <v>289</v>
       </c>
       <c r="M44" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N44" s="5" t="s">
-        <v>320</v>
+        <v>375</v>
       </c>
       <c r="O44" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="45" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A45" s="9" t="s">
         <v>122</v>
       </c>
@@ -4212,25 +4212,25 @@
         <v>99</v>
       </c>
       <c r="H45" s="11" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="I45" s="8" t="s">
-        <v>322</v>
+        <v>291</v>
       </c>
       <c r="J45" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K45" s="10" t="s">
-        <v>310</v>
+        <v>280</v>
       </c>
       <c r="L45" s="10" t="s">
-        <v>321</v>
+        <v>290</v>
       </c>
       <c r="M45" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N45" s="5" t="s">
-        <v>323</v>
+        <v>376</v>
       </c>
       <c r="O45" s="1" t="s">
         <v>143</v>
@@ -4259,31 +4259,31 @@
         <v>28</v>
       </c>
       <c r="H46" s="11" t="s">
-        <v>306</v>
+        <v>276</v>
       </c>
       <c r="I46" s="8" t="s">
-        <v>325</v>
+        <v>293</v>
       </c>
       <c r="J46" s="8" t="s">
-        <v>324</v>
+        <v>292</v>
       </c>
       <c r="K46" s="10" t="s">
-        <v>327</v>
+        <v>295</v>
       </c>
       <c r="L46" s="10" t="s">
-        <v>326</v>
+        <v>294</v>
       </c>
       <c r="M46" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N46" s="5" t="s">
-        <v>328</v>
+        <v>377</v>
       </c>
       <c r="O46" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="47" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A47" s="9" t="s">
         <v>126</v>
       </c>
@@ -4306,31 +4306,31 @@
         <v>99</v>
       </c>
       <c r="H47" s="11" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="I47" s="8" t="s">
-        <v>329</v>
+        <v>296</v>
       </c>
       <c r="J47" s="8" t="s">
-        <v>330</v>
+        <v>297</v>
       </c>
       <c r="K47" s="10" t="s">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="L47" s="10" t="s">
-        <v>331</v>
+        <v>298</v>
       </c>
       <c r="M47" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N47" s="5" t="s">
-        <v>332</v>
+        <v>378</v>
       </c>
       <c r="O47" s="1" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="48" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A48" s="9" t="s">
         <v>128</v>
       </c>
@@ -4353,25 +4353,25 @@
         <v>40</v>
       </c>
       <c r="H48" s="11" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="I48" s="8" t="s">
-        <v>333</v>
+        <v>299</v>
       </c>
       <c r="J48" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K48" s="10" t="s">
-        <v>312</v>
+        <v>282</v>
       </c>
       <c r="L48" s="10" t="s">
-        <v>334</v>
+        <v>300</v>
       </c>
       <c r="M48" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N48" s="5" t="s">
-        <v>335</v>
+        <v>379</v>
       </c>
       <c r="O48" s="1" t="s">
         <v>143</v>
@@ -4400,25 +4400,25 @@
         <v>28</v>
       </c>
       <c r="H49" s="11" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="I49" s="8" t="s">
-        <v>336</v>
+        <v>301</v>
       </c>
       <c r="J49" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K49" s="10" t="s">
-        <v>313</v>
+        <v>283</v>
       </c>
       <c r="L49" s="10" t="s">
-        <v>337</v>
+        <v>302</v>
       </c>
       <c r="M49" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N49" s="5" t="s">
-        <v>338</v>
+        <v>380</v>
       </c>
       <c r="O49" s="1" t="s">
         <v>143</v>
@@ -4429,7 +4429,7 @@
         <v>132</v>
       </c>
       <c r="B50" s="10" t="s">
-        <v>358</v>
+        <v>318</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>45</v>
@@ -4447,28 +4447,28 @@
         <v>28</v>
       </c>
       <c r="H50" s="11" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="I50" s="8" t="s">
-        <v>340</v>
+        <v>303</v>
       </c>
       <c r="J50" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K50" s="10" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="L50" s="10" t="s">
-        <v>341</v>
+        <v>304</v>
       </c>
       <c r="M50" s="1" t="s">
         <v>155</v>
       </c>
       <c r="N50" s="5" t="s">
-        <v>339</v>
+        <v>381</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>382</v>
+        <v>342</v>
       </c>
     </row>
     <row r="51" spans="1:15" ht="43.2" x14ac:dyDescent="0.3">
@@ -4494,25 +4494,25 @@
         <v>40</v>
       </c>
       <c r="H51" s="11" t="s">
+        <v>275</v>
+      </c>
+      <c r="I51" s="8" t="s">
         <v>305</v>
       </c>
-      <c r="I51" s="8" t="s">
-        <v>342</v>
-      </c>
       <c r="J51" s="8" t="s">
         <v>143</v>
       </c>
       <c r="K51" s="10" t="s">
-        <v>315</v>
+        <v>285</v>
       </c>
       <c r="L51" s="10" t="s">
-        <v>343</v>
+        <v>306</v>
       </c>
       <c r="M51" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N51" s="5" t="s">
-        <v>344</v>
+        <v>382</v>
       </c>
       <c r="O51" s="1" t="s">
         <v>143</v>
@@ -4523,7 +4523,7 @@
         <v>136</v>
       </c>
       <c r="B52" s="10" t="s">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>50</v>
@@ -4541,28 +4541,28 @@
         <v>40</v>
       </c>
       <c r="H52" s="11" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="I52" s="8" t="s">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="J52" s="8" t="s">
-        <v>362</v>
+        <v>322</v>
       </c>
       <c r="K52" s="10" t="s">
-        <v>363</v>
+        <v>323</v>
       </c>
       <c r="L52" s="10" t="s">
-        <v>364</v>
+        <v>324</v>
       </c>
       <c r="M52" s="1" t="s">
         <v>155</v>
       </c>
       <c r="N52" s="5" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
     </row>
     <row r="53" spans="1:15" ht="86.4" x14ac:dyDescent="0.3">
@@ -4588,25 +4588,25 @@
         <v>28</v>
       </c>
       <c r="H53" s="11" t="s">
+        <v>278</v>
+      </c>
+      <c r="I53" s="8" t="s">
+        <v>307</v>
+      </c>
+      <c r="J53" s="8" t="s">
+        <v>321</v>
+      </c>
+      <c r="K53" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="L53" s="10" t="s">
         <v>308</v>
-      </c>
-      <c r="I53" s="8" t="s">
-        <v>346</v>
-      </c>
-      <c r="J53" s="8" t="s">
-        <v>361</v>
-      </c>
-      <c r="K53" s="10" t="s">
-        <v>316</v>
-      </c>
-      <c r="L53" s="10" t="s">
-        <v>348</v>
       </c>
       <c r="M53" s="1" t="s">
         <v>156</v>
       </c>
       <c r="N53" s="5" t="s">
-        <v>347</v>
+        <v>384</v>
       </c>
       <c r="O53" s="1" t="s">
         <v>143</v>
@@ -4754,7 +4754,7 @@
         <v>19</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>349</v>
+        <v>309</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.3">
@@ -4770,7 +4770,7 @@
         <v>21</v>
       </c>
       <c r="B7" s="12" t="s">
-        <v>349</v>
+        <v>309</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.3">
@@ -4783,7 +4783,7 @@
     </row>
     <row r="11" spans="1:15" ht="31.2" x14ac:dyDescent="0.6">
       <c r="A11" s="39" t="s">
-        <v>351</v>
+        <v>311</v>
       </c>
       <c r="B11" s="39"/>
       <c r="C11" s="39"/>
@@ -4805,10 +4805,10 @@
         <v>9</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>352</v>
+        <v>312</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>353</v>
+        <v>313</v>
       </c>
       <c r="D13" s="13" t="s">
         <v>10</v>
@@ -4849,10 +4849,10 @@
     </row>
     <row r="14" spans="1:15" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>356</v>
+        <v>316</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>63</v>
@@ -4873,33 +4873,33 @@
         <v>28</v>
       </c>
       <c r="I14" s="8" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="J14" s="8" t="s">
+        <v>161</v>
+      </c>
+      <c r="K14" s="8" t="s">
+        <v>314</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>164</v>
+      </c>
+      <c r="M14" s="8" t="s">
         <v>162</v>
       </c>
-      <c r="K14" s="8" t="s">
-        <v>354</v>
-      </c>
-      <c r="L14" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="M14" s="8" t="s">
-        <v>163</v>
-      </c>
       <c r="N14" s="1" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="O14" s="5" t="s">
-        <v>166</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15" spans="1:15" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>381</v>
+        <v>341</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>384</v>
+        <v>344</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>102</v>
@@ -4920,33 +4920,33 @@
         <v>99</v>
       </c>
       <c r="I15" s="18" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="J15" s="16" t="s">
-        <v>260</v>
+        <v>239</v>
       </c>
       <c r="K15" s="16" t="s">
         <v>151</v>
       </c>
       <c r="L15" s="14" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="M15" s="14" t="s">
-        <v>261</v>
+        <v>240</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="O15" s="17" t="s">
-        <v>262</v>
+        <v>366</v>
       </c>
     </row>
     <row r="16" spans="1:15" ht="144" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>382</v>
+        <v>342</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>357</v>
+        <v>317</v>
       </c>
       <c r="C16" s="19" t="s">
         <v>132</v>
@@ -4967,33 +4967,33 @@
         <v>28</v>
       </c>
       <c r="I16" s="22" t="s">
-        <v>308</v>
+        <v>278</v>
       </c>
       <c r="J16" s="23" t="s">
-        <v>340</v>
+        <v>303</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>143</v>
       </c>
       <c r="L16" s="20" t="s">
-        <v>314</v>
+        <v>284</v>
       </c>
       <c r="M16" s="20" t="s">
-        <v>341</v>
+        <v>304</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="O16" s="24" t="s">
-        <v>339</v>
+        <v>381</v>
       </c>
     </row>
     <row r="17" spans="1:15" ht="100.8" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>383</v>
+        <v>343</v>
       </c>
       <c r="B17" s="34" t="s">
-        <v>365</v>
+        <v>325</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>136</v>
@@ -5014,25 +5014,25 @@
         <v>40</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>305</v>
+        <v>275</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>360</v>
+        <v>320</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>362</v>
+        <v>322</v>
       </c>
       <c r="L17" s="10" t="s">
-        <v>363</v>
+        <v>323</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>364</v>
+        <v>324</v>
       </c>
       <c r="N17" s="33" t="s">
-        <v>355</v>
+        <v>315</v>
       </c>
       <c r="O17" s="37" t="s">
-        <v>345</v>
+        <v>383</v>
       </c>
     </row>
     <row r="18" spans="1:15" s="25" customFormat="1" x14ac:dyDescent="0.3">
